--- a/translations/welsh-translations/12-cso-statement-view.xlsx
+++ b/translations/welsh-translations/12-cso-statement-view.xlsx
@@ -678,7 +678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -698,7 +698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -718,7 +718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
